--- a/data/trans_camb/P1803_2016_2023-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1803_2016_2023-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,81</t>
+          <t>8,22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>7,07</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 12,04</t>
+          <t>1,09; 10,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 15,7</t>
+          <t>2,5; 13,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,08</t>
+          <t>3,14; 10,61</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,57; 225,42</t>
+          <t>8,95; 195,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 180,53</t>
+          <t>12,78; 150,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,64; 155,67</t>
+          <t>25,9; 136,29</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,58</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,38</t>
+          <t>1,05; 7,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,46</t>
+          <t>2,55; 8,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,92</t>
+          <t>2,43; 6,57</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>182,76%</t>
+          <t>170,46%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>213,87%</t>
+          <t>206,94%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>199,23%</t>
+          <t>190,91%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,07; 593,28</t>
+          <t>21,94; 647,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,94; 493,86</t>
+          <t>52,92; 480,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,71; 386,18</t>
+          <t>72,49; 365,45</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,91</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,52</t>
+          <t>9,32</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,7</t>
+          <t>5,54; 12,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,73</t>
+          <t>6,53; 13,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 12,16</t>
+          <t>7,07; 11,88</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>539,91%</t>
+          <t>527,76%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>477,07%</t>
+          <t>466,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504,76%</t>
+          <t>494,06%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>144,56; 1805,16</t>
+          <t>164,87; 1819,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>170,16; 1333,68</t>
+          <t>174,5; 1215,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>234,44; 1115,44</t>
+          <t>229,0; 1024,34</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,36</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 8,49</t>
+          <t>-2,34; 7,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 6,32</t>
+          <t>0,47; 8,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,83</t>
+          <t>0,18; 6,12</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 150,86</t>
+          <t>-25,43; 128,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 119,33</t>
+          <t>2,02; 156,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 100,68</t>
+          <t>0,92; 101,27</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,98</t>
+          <t>-1,57; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,04</t>
+          <t>-4,23; 1,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,69</t>
+          <t>-1,93; 2,49</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-22,73%</t>
+          <t>-24,62%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,67; 707,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,92; 110,68</t>
+          <t>-70,67; 115,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 136,56</t>
+          <t>-46,07; 137,01</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,97</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,33</t>
+          <t>-4,29; 5,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,31</t>
+          <t>4,94; 13,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,04</t>
+          <t>1,86; 8,04</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>205,7%</t>
+          <t>207,22%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 103,5</t>
+          <t>-42,84; 101,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68,24; 480,67</t>
+          <t>60,1; 456,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25,15; 176,28</t>
+          <t>18,96; 173,83</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>7,79</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>8,11</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,79</t>
+          <t>4,22; 11,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,48</t>
+          <t>5,87; 11,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,73</t>
+          <t>5,96; 10,34</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>151,05%</t>
+          <t>144,89%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>103,27%</t>
+          <t>154,06%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>123,74%</t>
+          <t>149,94%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>60,24; 302,77</t>
+          <t>58,98; 284,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 214,74</t>
+          <t>78,14; 267,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38,24; 209,19</t>
+          <t>90,73; 230,51</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>24,06</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11,46</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 62,75</t>
+          <t>-3,36; 0,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -2,34</t>
+          <t>-6,52; -2,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 42,76</t>
+          <t>-4,53; -1,65</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>609,81%</t>
+          <t>-41,5%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-65,15%</t>
+          <t>-63,96%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>213,71%</t>
+          <t>-55,95%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 2275,4</t>
+          <t>-68,01; 13,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-77,83; -42,38</t>
+          <t>-77,09; -41,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 849,65</t>
+          <t>-70,73; -35,49</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,48; 29,72</t>
+          <t>2,24; 4,72</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,25</t>
+          <t>3,26; 5,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,54; 18,48</t>
+          <t>3,07; 4,74</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>224,6%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>138,74%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>73,46; 708,35</t>
+          <t>44,5; 115,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>35,32; 104,21</t>
+          <t>54,76; 113,59</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>68,95; 388,12</t>
+          <t>55,54; 100,64</t>
         </is>
       </c>
     </row>
